--- a/artfynd/A 65218-2023 artfynd.xlsx
+++ b/artfynd/A 65218-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65218-2023 artfynd.xlsx
+++ b/artfynd/A 65218-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1169,6 +1169,327 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122537859</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98211</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nordkölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>478646</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6932927</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122537950</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97165</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nordkölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>478608</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6932919</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122539452</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78652</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nordkölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>478646</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6932927</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 65218-2023 artfynd.xlsx
+++ b/artfynd/A 65218-2023 artfynd.xlsx
@@ -1171,10 +1171,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122537859</v>
+        <v>122537950</v>
       </c>
       <c r="B6" t="n">
-        <v>98211</v>
+        <v>97178</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,20 +1183,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1206,10 +1211,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478646</v>
+        <v>478608</v>
       </c>
       <c r="R6" t="n">
-        <v>6932927</v>
+        <v>6932919</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122537950</v>
+        <v>122537859</v>
       </c>
       <c r="B7" t="n">
-        <v>97165</v>
+        <v>98224</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,20 +1295,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1313,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478608</v>
+        <v>478646</v>
       </c>
       <c r="R7" t="n">
-        <v>6932919</v>
+        <v>6932927</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1385,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122539452</v>
+        <v>122570061</v>
       </c>
       <c r="B8" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,6 +1412,11 @@
       </c>
       <c r="E8" t="n">
         <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>

--- a/artfynd/A 65218-2023 artfynd.xlsx
+++ b/artfynd/A 65218-2023 artfynd.xlsx
@@ -1174,7 +1174,7 @@
         <v>122537950</v>
       </c>
       <c r="B6" t="n">
-        <v>97178</v>
+        <v>97191</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>122537859</v>
       </c>
       <c r="B7" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 65218-2023 artfynd.xlsx
+++ b/artfynd/A 65218-2023 artfynd.xlsx
@@ -1171,10 +1171,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122537950</v>
+        <v>122537859</v>
       </c>
       <c r="B6" t="n">
-        <v>97191</v>
+        <v>98240</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,25 +1183,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478608</v>
+        <v>478646</v>
       </c>
       <c r="R6" t="n">
-        <v>6932919</v>
+        <v>6932927</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1283,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122537859</v>
+        <v>122537950</v>
       </c>
       <c r="B7" t="n">
-        <v>98237</v>
+        <v>97194</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,25 +1295,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478646</v>
+        <v>478608</v>
       </c>
       <c r="R7" t="n">
-        <v>6932927</v>
+        <v>6932919</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 65218-2023 artfynd.xlsx
+++ b/artfynd/A 65218-2023 artfynd.xlsx
@@ -1174,7 +1174,7 @@
         <v>122537859</v>
       </c>
       <c r="B6" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>122537950</v>
       </c>
       <c r="B7" t="n">
-        <v>97301</v>
+        <v>97309</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>122570061</v>
       </c>
       <c r="B8" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 65218-2023 artfynd.xlsx
+++ b/artfynd/A 65218-2023 artfynd.xlsx
@@ -1174,7 +1174,7 @@
         <v>122537859</v>
       </c>
       <c r="B6" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>122537950</v>
       </c>
       <c r="B7" t="n">
-        <v>97309</v>
+        <v>97311</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 65218-2023 artfynd.xlsx
+++ b/artfynd/A 65218-2023 artfynd.xlsx
@@ -1171,10 +1171,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122537859</v>
+        <v>122537950</v>
       </c>
       <c r="B6" t="n">
-        <v>98357</v>
+        <v>97311</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,25 +1183,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478646</v>
+        <v>478608</v>
       </c>
       <c r="R6" t="n">
-        <v>6932927</v>
+        <v>6932919</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1283,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122537950</v>
+        <v>122537859</v>
       </c>
       <c r="B7" t="n">
-        <v>97311</v>
+        <v>98357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,25 +1295,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478608</v>
+        <v>478646</v>
       </c>
       <c r="R7" t="n">
-        <v>6932919</v>
+        <v>6932927</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
